--- a/files/九龙-红磡-悦麓.xlsx
+++ b/files/九龙-红磡-悦麓.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="悦麓 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -612,7 +473,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -908,7 +769,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -954,7 +815,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1000,7 +861,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1046,7 +907,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1092,7 +953,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1138,7 +999,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1184,7 +1045,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1230,7 +1091,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1276,7 +1137,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1322,7 +1183,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1414,7 +1275,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1660,7 +1521,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1706,7 +1567,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1752,7 +1613,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1798,7 +1659,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1844,7 +1705,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1890,7 +1751,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1936,7 +1797,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2032,7 +1893,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2078,7 +1939,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2124,7 +1985,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2170,7 +2031,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2216,7 +2077,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2262,7 +2123,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2308,7 +2169,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2354,7 +2215,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2400,7 +2261,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2446,7 +2307,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2492,7 +2353,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2538,7 +2399,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2584,7 +2445,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2726,7 +2587,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2872,7 +2733,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2968,7 +2829,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3014,7 +2875,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3060,7 +2921,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3106,7 +2967,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3152,7 +3013,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3198,7 +3059,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3244,7 +3105,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3290,7 +3151,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3336,7 +3197,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3382,7 +3243,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3428,7 +3289,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3474,7 +3335,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3520,7 +3381,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3566,7 +3427,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3612,7 +3473,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3658,7 +3519,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3704,7 +3565,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3750,7 +3611,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3796,7 +3657,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3842,7 +3703,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4118,7 +3979,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4164,7 +4025,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4210,7 +4071,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4256,7 +4117,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4302,7 +4163,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4398,7 +4259,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4444,7 +4305,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4536,7 +4397,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4558,930 +4419,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>悦麓 - 悦麓 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>83 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>18 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>61 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 288呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 267呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 266呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 252呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 288呎 (1房)
-$724万
-$25,147/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 267呎 (1房)
-$666万
-$24,950/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 266呎 (1房)
-$650万
-$24,451/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 252呎 (1房)
-$597万
-$23,703/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 288呎 (1房)
-$660万
-$22,901/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 267呎 (1房)
-$665万
-$24,913/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 266呎 (1房)
-$605万
-$22,736/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 252呎 (1房)
-$568万
-$22,541/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 288呎 (1房)
-$656万
-$22,787/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 267呎 (1房)
-$683万
-$25,588/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 266呎 (1房)
-$615万
-$23,137/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 252呎 (1房)
-$565万
-$22,429/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 288呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 267呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 266呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 252呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 288呎 (1房)
-$614万
-$21,334/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 267呎 (1房)
-$590万
-$22,104/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 266呎 (1房)
-$609万
-$22,907/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 252呎 (1房)
-$560万
-$22,206/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 291呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 265呎 (1房)
-$603万
-$22,742/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 266呎 (1房)
-$606万
-$22,794/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 252呎 (1房)
-$557万
-$22,096/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 189呎 (开放式)
-$388万
-$20,504/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 196呎 (开放式)
-$358万
-$18,286/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 248呎 (1房)
-$560万
-$22,576/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 267呎 (1房)
-$591万
-$22,125/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 252呎 (1房)
-$540万
-$21,447/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 189呎 (开放式)
-$367万
-$19,417/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 196呎 (开放式)
-$353万
-$18,017/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 248呎 (1房)
-$552万
-$22,242/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 267呎 (1房)
-$582万
-$21,798/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 252呎 (1房)
-$532万
-$21,131/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 189呎 (开放式)
-$491万
-$26,000/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>B | 194呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 248呎 (1房)
-$514万
-$20,723/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 267呎 (1房)
-$530万
-$19,857/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 252呎 (1房)
-$485万
-$19,249/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 201呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 283呎 (1房)
-$577万
-$20,390/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 266呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 268呎 (1房)
-$590万
-$22,030/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 201呎 (开放式)
-$373万
-$18,569/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 283呎 (1房)
-$602万
-$21,271/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 264呎 (1房)
-$562万
-$21,271/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 266呎 (1房)
-$554万
-$20,845/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 268呎 (1房)
-$542万
-$20,207/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 203呎 (开放式)
-$355万
-$17,493/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 283呎 (1房)
-$548万
-$19,377/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 282呎 (1房)
-$546万
-$19,377/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 267呎 (1房)
-$507万
-$18,990/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 304呎 (1房)
-$579万
-$19,036/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 203呎 (开放式)
-$346万
-$17,045/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 283呎 (1房)
-$540万
-$19,090/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 282呎 (1房)
-$538万
-$19,091/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 267呎 (1房)
-$500万
-$18,709/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 304呎 (1房)
-$564万
-$18,548/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 203呎 (开放式)
-$340万
-$16,739/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 283呎 (1房)
-$532万
-$18,808/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 282呎 (1房)
-$530万
-$18,809/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 267呎 (1房)
-$492万
-$18,433/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 304呎 (1房)
-$589万
-$19,371/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 203呎 (开放式)
-$414万
-$20,380/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 283呎 (1房)
-$623万
-$22,008/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 282呎 (1房)
-$621万
-$22,008/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 267呎 (1房)
-$586万
-$21,936/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 304呎 (1房)
-$656万
-$21,580/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 203呎 (开放式)
-$325万
-$15,988/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 283呎 (1房)
-$521万
-$18,396/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 282呎 (1房)
-$519万
-$18,396/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 267呎 (1房)
-$481万
-$18,028/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 304呎 (1房)
-$531万
-$17,476/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 166呎 (开放式)
-$426万
-$25,688/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 245呎 (1房)
-$661万
-$26,980/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 244呎 (1房)
-$572万
-$23,425/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 229呎 (1房)
-$553万
-$24,130/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 267呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-红磡-悦麓.xlsx
+++ b/files/九龙-红磡-悦麓.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="悦麓" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +148,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +229,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4419,4 +4607,930 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>悦麓 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 288呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 267呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 266呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 252呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 288呎 (1房)
+$724万
+$25,147/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 267呎 (1房)
+$666万
+$24,950/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 266呎 (1房)
+$650万
+$24,451/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 252呎 (1房)
+$597万
+$23,703/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 288呎 (1房)
+$660万
+$22,901/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 267呎 (1房)
+$665万
+$24,913/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 266呎 (1房)
+$605万
+$22,736/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 252呎 (1房)
+$568万
+$22,541/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 288呎 (1房)
+$656万
+$22,787/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 267呎 (1房)
+$683万
+$25,588/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 266呎 (1房)
+$615万
+$23,137/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 252呎 (1房)
+$565万
+$22,429/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 288呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 267呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 266呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 252呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 288呎 (1房)
+$614万
+$21,334/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 267呎 (1房)
+$590万
+$22,104/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 266呎 (1房)
+$609万
+$22,907/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 252呎 (1房)
+$560万
+$22,206/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 291呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 265呎 (1房)
+$603万
+$22,742/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 266呎 (1房)
+$606万
+$22,794/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 252呎 (1房)
+$557万
+$22,096/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 189呎 (开放式)
+$388万
+$20,504/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 196呎 (开放式)
+$358万
+$18,286/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 248呎 (1房)
+$560万
+$22,576/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 267呎 (1房)
+$591万
+$22,125/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 252呎 (1房)
+$540万
+$21,447/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 189呎 (开放式)
+$367万
+$19,417/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 196呎 (开放式)
+$353万
+$18,017/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 248呎 (1房)
+$552万
+$22,242/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 267呎 (1房)
+$582万
+$21,798/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 252呎 (1房)
+$532万
+$21,131/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 189呎 (开放式)
+$491万
+$26,000/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>B | 194呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 248呎 (1房)
+$514万
+$20,723/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 267呎 (1房)
+$530万
+$19,857/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 252呎 (1房)
+$485万
+$19,249/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>A | 201呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 283呎 (1房)
+$577万
+$20,390/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 266呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 268呎 (1房)
+$590万
+$22,030/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 201呎 (开放式)
+$373万
+$18,569/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 283呎 (1房)
+$602万
+$21,271/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$562万
+$21,271/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 266呎 (1房)
+$554万
+$20,845/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 268呎 (1房)
+$542万
+$20,207/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 203呎 (开放式)
+$355万
+$17,493/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 283呎 (1房)
+$548万
+$19,377/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 282呎 (1房)
+$546万
+$19,377/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 267呎 (1房)
+$507万
+$18,990/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 304呎 (1房)
+$579万
+$19,036/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 203呎 (开放式)
+$346万
+$17,045/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 283呎 (1房)
+$540万
+$19,090/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 282呎 (1房)
+$538万
+$19,091/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 267呎 (1房)
+$500万
+$18,709/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 304呎 (1房)
+$564万
+$18,548/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 203呎 (开放式)
+$340万
+$16,739/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 283呎 (1房)
+$532万
+$18,808/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 282呎 (1房)
+$530万
+$18,809/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 267呎 (1房)
+$492万
+$18,433/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 304呎 (1房)
+$589万
+$19,371/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 203呎 (开放式)
+$414万
+$20,380/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 283呎 (1房)
+$623万
+$22,008/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 282呎 (1房)
+$621万
+$22,008/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 267呎 (1房)
+$586万
+$21,936/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 304呎 (1房)
+$656万
+$21,580/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 203呎 (开放式)
+$325万
+$15,988/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 283呎 (1房)
+$521万
+$18,396/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 282呎 (1房)
+$519万
+$18,396/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 267呎 (1房)
+$481万
+$18,028/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 304呎 (1房)
+$531万
+$17,476/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 166呎 (开放式)
+$426万
+$25,688/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 245呎 (1房)
+$661万
+$26,980/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 244呎 (1房)
+$572万
+$23,425/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 229呎 (1房)
+$553万
+$24,130/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 267呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-红磡-悦麓.xlsx
+++ b/files/九龙-红磡-悦麓.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -665,6 +665,10 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -722,6 +726,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -772,6 +796,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -822,6 +866,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -872,6 +936,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -922,6 +1006,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -968,6 +1072,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1014,6 +1138,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1060,6 +1204,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1106,6 +1270,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1152,6 +1336,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1198,6 +1402,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1244,6 +1468,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1290,6 +1534,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1336,6 +1600,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1382,6 +1666,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1428,6 +1732,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1474,6 +1798,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1524,6 +1868,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1574,6 +1938,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1624,6 +2008,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1674,6 +2078,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1720,6 +2144,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1766,6 +2210,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1812,6 +2276,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1858,6 +2342,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1904,6 +2408,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1950,6 +2474,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1996,6 +2540,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2046,6 +2610,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2092,6 +2676,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2138,6 +2742,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2184,6 +2808,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2230,6 +2874,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2276,6 +2940,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2322,6 +3006,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2368,6 +3072,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2414,6 +3138,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2460,6 +3204,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2506,6 +3270,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2552,6 +3336,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2598,6 +3402,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2644,6 +3468,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2694,6 +3538,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2740,6 +3604,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2786,6 +3670,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2836,6 +3740,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2886,6 +3810,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2932,6 +3876,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2982,6 +3946,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3028,6 +4012,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3074,6 +4078,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3120,6 +4144,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3166,6 +4210,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3212,6 +4276,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3258,6 +4342,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3304,6 +4408,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3350,6 +4474,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3396,6 +4540,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3442,6 +4606,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3488,6 +4672,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3534,6 +4738,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3580,6 +4804,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3626,6 +4870,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3672,6 +4936,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3718,6 +5002,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3764,6 +5068,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3810,6 +5134,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3856,6 +5200,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3902,6 +5266,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3948,6 +5332,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3994,6 +5398,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4040,6 +5464,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4086,6 +5530,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4132,6 +5596,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4178,6 +5662,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4224,6 +5728,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4270,6 +5794,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4316,6 +5860,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4362,6 +5926,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4412,6 +5996,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4458,6 +6062,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4504,6 +6128,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4550,6 +6194,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4596,13 +6260,33 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4780,7 +6464,7 @@
           <t>A | 288呎 (1房)
 $724万
 $25,147/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -4788,7 +6472,7 @@
           <t>B | 267呎 (1房)
 $666万
 $24,950/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -4796,7 +6480,7 @@
           <t>C | 266呎 (1房)
 $650万
 $24,451/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -4804,7 +6488,7 @@
           <t>D | 252呎 (1房)
 $597万
 $23,703/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr"/>
@@ -4820,7 +6504,7 @@
           <t>A | 288呎 (1房)
 $660万
 $22,901/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -4828,7 +6512,7 @@
           <t>B | 267呎 (1房)
 $665万
 $24,913/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -4836,7 +6520,7 @@
           <t>C | 266呎 (1房)
 $605万
 $22,736/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -4844,7 +6528,7 @@
           <t>D | 252呎 (1房)
 $568万
 $22,541/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr"/>
@@ -4860,7 +6544,7 @@
           <t>A | 288呎 (1房)
 $656万
 $22,787/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -4876,7 +6560,7 @@
           <t>C | 266呎 (1房)
 $615万
 $23,137/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -4884,7 +6568,7 @@
           <t>D | 252呎 (1房)
 $565万
 $22,429/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr"/>
@@ -4940,7 +6624,7 @@
           <t>A | 288呎 (1房)
 $614万
 $21,334/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -4948,7 +6632,7 @@
           <t>B | 267呎 (1房)
 $590万
 $22,104/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -4956,7 +6640,7 @@
           <t>C | 266呎 (1房)
 $609万
 $22,907/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -4964,7 +6648,7 @@
           <t>D | 252呎 (1房)
 $560万
 $22,206/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -4988,7 +6672,7 @@
           <t>B | 265呎 (1房)
 $603万
 $22,742/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -4996,7 +6680,7 @@
           <t>C | 266呎 (1房)
 $606万
 $22,794/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -5004,7 +6688,7 @@
           <t>D | 252呎 (1房)
 $557万
 $22,096/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -5020,7 +6704,7 @@
           <t>A | 189呎 (开放式)
 $388万
 $20,504/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -5028,7 +6712,7 @@
           <t>B | 196呎 (开放式)
 $358万
 $18,286/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -5036,7 +6720,7 @@
           <t>C | 248呎 (1房)
 $560万
 $22,576/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -5044,7 +6728,7 @@
           <t>D | 267呎 (1房)
 $591万
 $22,125/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -5052,7 +6736,7 @@
           <t>E | 252呎 (1房)
 $540万
 $21,447/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
     </row>
@@ -5067,7 +6751,7 @@
           <t>A | 189呎 (开放式)
 $367万
 $19,417/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -5075,7 +6759,7 @@
           <t>B | 196呎 (开放式)
 $353万
 $18,017/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -5083,7 +6767,7 @@
           <t>C | 248呎 (1房)
 $552万
 $22,242/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -5091,7 +6775,7 @@
           <t>D | 267呎 (1房)
 $582万
 $21,798/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -5099,7 +6783,7 @@
           <t>E | 252呎 (1房)
 $532万
 $21,131/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -5130,7 +6814,7 @@
           <t>C | 248呎 (1房)
 $514万
 $20,723/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -5138,7 +6822,7 @@
           <t>D | 267呎 (1房)
 $530万
 $19,857/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -5146,7 +6830,7 @@
           <t>E | 252呎 (1房)
 $485万
 $19,249/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
     </row>
@@ -5169,7 +6853,7 @@
           <t>B | 283呎 (1房)
 $577万
 $20,390/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -5193,7 +6877,7 @@
           <t>E | 268呎 (1房)
 $590万
 $22,030/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -5208,7 +6892,7 @@
           <t>A | 201呎 (开放式)
 $373万
 $18,569/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -5216,7 +6900,7 @@
           <t>B | 283呎 (1房)
 $602万
 $21,271/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -5224,7 +6908,7 @@
           <t>C | 264呎 (1房)
 $562万
 $21,271/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -5232,7 +6916,7 @@
           <t>D | 266呎 (1房)
 $554万
 $20,845/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -5240,7 +6924,7 @@
           <t>E | 268呎 (1房)
 $542万
 $20,207/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -5255,7 +6939,7 @@
           <t>A | 203呎 (开放式)
 $355万
 $17,493/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -5263,7 +6947,7 @@
           <t>B | 283呎 (1房)
 $548万
 $19,377/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -5271,7 +6955,7 @@
           <t>C | 282呎 (1房)
 $546万
 $19,377/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -5279,7 +6963,7 @@
           <t>D | 267呎 (1房)
 $507万
 $18,990/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -5287,7 +6971,7 @@
           <t>E | 304呎 (1房)
 $579万
 $19,036/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
     </row>
@@ -5302,7 +6986,7 @@
           <t>A | 203呎 (开放式)
 $346万
 $17,045/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -5310,7 +6994,7 @@
           <t>B | 283呎 (1房)
 $540万
 $19,090/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -5318,7 +7002,7 @@
           <t>C | 282呎 (1房)
 $538万
 $19,091/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -5326,7 +7010,7 @@
           <t>D | 267呎 (1房)
 $500万
 $18,709/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -5334,7 +7018,7 @@
           <t>E | 304呎 (1房)
 $564万
 $18,548/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -5349,7 +7033,7 @@
           <t>A | 203呎 (开放式)
 $340万
 $16,739/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -5357,7 +7041,7 @@
           <t>B | 283呎 (1房)
 $532万
 $18,808/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -5365,7 +7049,7 @@
           <t>C | 282呎 (1房)
 $530万
 $18,809/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -5373,7 +7057,7 @@
           <t>D | 267呎 (1房)
 $492万
 $18,433/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -5381,7 +7065,7 @@
           <t>E | 304呎 (1房)
 $589万
 $19,371/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
     </row>
@@ -5443,7 +7127,7 @@
           <t>A | 203呎 (开放式)
 $325万
 $15,988/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -5451,7 +7135,7 @@
           <t>B | 283呎 (1房)
 $521万
 $18,396/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -5459,7 +7143,7 @@
           <t>C | 282呎 (1房)
 $519万
 $18,396/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -5467,7 +7151,7 @@
           <t>D | 267呎 (1房)
 $481万
 $18,028/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -5475,7 +7159,7 @@
           <t>E | 304呎 (1房)
 $531万
 $17,476/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
     </row>
@@ -5490,7 +7174,7 @@
           <t>A | 166呎 (开放式)
 $426万
 $25,688/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -5506,7 +7190,7 @@
           <t>C | 244呎 (1房)
 $572万
 $23,425/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -5514,7 +7198,7 @@
           <t>D | 229呎 (1房)
 $553万
 $24,130/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">

--- a/files/九龙-红磡-悦麓.xlsx
+++ b/files/九龙-红磡-悦麓.xlsx
@@ -5448,12 +5448,12 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7091,12 +7091,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 282呎 (1房)
 $621万
 $22,008/呎
-(在售)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">

--- a/files/九龙-红磡-悦麓.xlsx
+++ b/files/九龙-红磡-悦麓.xlsx
@@ -6464,7 +6464,7 @@
           <t>A | 288呎 (1房)
 $724万
 $25,147/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -6472,7 +6472,7 @@
           <t>B | 267呎 (1房)
 $666万
 $24,950/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -6480,7 +6480,7 @@
           <t>C | 266呎 (1房)
 $650万
 $24,451/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -6488,7 +6488,7 @@
           <t>D | 252呎 (1房)
 $597万
 $23,703/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr"/>
@@ -6504,7 +6504,7 @@
           <t>A | 288呎 (1房)
 $660万
 $22,901/呎
-(26年-03月-09日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -6512,7 +6512,7 @@
           <t>B | 267呎 (1房)
 $665万
 $24,913/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -6520,7 +6520,7 @@
           <t>C | 266呎 (1房)
 $605万
 $22,736/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -6528,7 +6528,7 @@
           <t>D | 252呎 (1房)
 $568万
 $22,541/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr"/>
@@ -6544,7 +6544,7 @@
           <t>A | 288呎 (1房)
 $656万
 $22,787/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -6560,7 +6560,7 @@
           <t>C | 266呎 (1房)
 $615万
 $23,137/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -6568,7 +6568,7 @@
           <t>D | 252呎 (1房)
 $565万
 $22,429/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr"/>
@@ -6624,7 +6624,7 @@
           <t>A | 288呎 (1房)
 $614万
 $21,334/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -6632,7 +6632,7 @@
           <t>B | 267呎 (1房)
 $590万
 $22,104/呎
-(26年-02月-19日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -6640,7 +6640,7 @@
           <t>C | 266呎 (1房)
 $609万
 $22,907/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -6648,7 +6648,7 @@
           <t>D | 252呎 (1房)
 $560万
 $22,206/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -6672,7 +6672,7 @@
           <t>B | 265呎 (1房)
 $603万
 $22,742/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -6680,7 +6680,7 @@
           <t>C | 266呎 (1房)
 $606万
 $22,794/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -6688,7 +6688,7 @@
           <t>D | 252呎 (1房)
 $557万
 $22,096/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -6704,7 +6704,7 @@
           <t>A | 189呎 (开放式)
 $388万
 $20,504/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -6712,7 +6712,7 @@
           <t>B | 196呎 (开放式)
 $358万
 $18,286/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -6720,7 +6720,7 @@
           <t>C | 248呎 (1房)
 $560万
 $22,576/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -6728,7 +6728,7 @@
           <t>D | 267呎 (1房)
 $591万
 $22,125/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -6736,7 +6736,7 @@
           <t>E | 252呎 (1房)
 $540万
 $21,447/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
           <t>A | 189呎 (开放式)
 $367万
 $19,417/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -6759,7 +6759,7 @@
           <t>B | 196呎 (开放式)
 $353万
 $18,017/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -6767,7 +6767,7 @@
           <t>C | 248呎 (1房)
 $552万
 $22,242/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -6775,7 +6775,7 @@
           <t>D | 267呎 (1房)
 $582万
 $21,798/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -6783,7 +6783,7 @@
           <t>E | 252呎 (1房)
 $532万
 $21,131/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
           <t>C | 248呎 (1房)
 $514万
 $20,723/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -6822,7 +6822,7 @@
           <t>D | 267呎 (1房)
 $530万
 $19,857/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -6830,7 +6830,7 @@
           <t>E | 252呎 (1房)
 $485万
 $19,249/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
           <t>B | 283呎 (1房)
 $577万
 $20,390/呎
-(26年-02月-19日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -6877,7 +6877,7 @@
           <t>E | 268呎 (1房)
 $590万
 $22,030/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
           <t>A | 201呎 (开放式)
 $373万
 $18,569/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -6900,7 +6900,7 @@
           <t>B | 283呎 (1房)
 $602万
 $21,271/呎
-(26年-02月-19日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -6908,7 +6908,7 @@
           <t>C | 264呎 (1房)
 $562万
 $21,271/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -6916,7 +6916,7 @@
           <t>D | 266呎 (1房)
 $554万
 $20,845/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -6924,7 +6924,7 @@
           <t>E | 268呎 (1房)
 $542万
 $20,207/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -6939,7 +6939,7 @@
           <t>A | 203呎 (开放式)
 $355万
 $17,493/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -6947,7 +6947,7 @@
           <t>B | 283呎 (1房)
 $548万
 $19,377/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -6955,7 +6955,7 @@
           <t>C | 282呎 (1房)
 $546万
 $19,377/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -6963,7 +6963,7 @@
           <t>D | 267呎 (1房)
 $507万
 $18,990/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -6971,7 +6971,7 @@
           <t>E | 304呎 (1房)
 $579万
 $19,036/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
           <t>A | 203呎 (开放式)
 $346万
 $17,045/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -6994,7 +6994,7 @@
           <t>B | 283呎 (1房)
 $540万
 $19,090/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -7002,7 +7002,7 @@
           <t>C | 282呎 (1房)
 $538万
 $19,091/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -7010,7 +7010,7 @@
           <t>D | 267呎 (1房)
 $500万
 $18,709/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -7018,7 +7018,7 @@
           <t>E | 304呎 (1房)
 $564万
 $18,548/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7033,7 @@
           <t>A | 203呎 (开放式)
 $340万
 $16,739/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -7041,7 +7041,7 @@
           <t>B | 283呎 (1房)
 $532万
 $18,808/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7049,7 +7049,7 @@
           <t>C | 282呎 (1房)
 $530万
 $18,809/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -7057,7 +7057,7 @@
           <t>D | 267呎 (1房)
 $492万
 $18,433/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -7065,7 +7065,7 @@
           <t>E | 304呎 (1房)
 $589万
 $19,371/呎
-(26年-03月-15日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
           <t>C | 282呎 (1房)
 $621万
 $22,008/呎
-(26年-07月-17日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -7127,7 +7127,7 @@
           <t>A | 203呎 (开放式)
 $325万
 $15,988/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -7135,7 +7135,7 @@
           <t>B | 283呎 (1房)
 $521万
 $18,396/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -7143,7 +7143,7 @@
           <t>C | 282呎 (1房)
 $519万
 $18,396/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -7151,7 +7151,7 @@
           <t>D | 267呎 (1房)
 $481万
 $18,028/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -7159,7 +7159,7 @@
           <t>E | 304呎 (1房)
 $531万
 $17,476/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
           <t>A | 166呎 (开放式)
 $426万
 $25,688/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -7190,7 +7190,7 @@
           <t>C | 244呎 (1房)
 $572万
 $23,425/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -7198,7 +7198,7 @@
           <t>D | 229呎 (1房)
 $553万
 $24,130/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">

--- a/files/九龙-红磡-悦麓.xlsx
+++ b/files/九龙-红磡-悦麓.xlsx
@@ -6464,7 +6464,7 @@
           <t>A | 288呎 (1房)
 $724万
 $25,147/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -6472,7 +6472,7 @@
           <t>B | 267呎 (1房)
 $666万
 $24,950/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -6480,7 +6480,7 @@
           <t>C | 266呎 (1房)
 $650万
 $24,451/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -6488,7 +6488,7 @@
           <t>D | 252呎 (1房)
 $597万
 $23,703/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr"/>
@@ -6504,7 +6504,7 @@
           <t>A | 288呎 (1房)
 $660万
 $22,901/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -6512,7 +6512,7 @@
           <t>B | 267呎 (1房)
 $665万
 $24,913/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -6520,7 +6520,7 @@
           <t>C | 266呎 (1房)
 $605万
 $22,736/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -6528,7 +6528,7 @@
           <t>D | 252呎 (1房)
 $568万
 $22,541/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr"/>
@@ -6544,7 +6544,7 @@
           <t>A | 288呎 (1房)
 $656万
 $22,787/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -6560,7 +6560,7 @@
           <t>C | 266呎 (1房)
 $615万
 $23,137/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -6568,7 +6568,7 @@
           <t>D | 252呎 (1房)
 $565万
 $22,429/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr"/>
@@ -6624,7 +6624,7 @@
           <t>A | 288呎 (1房)
 $614万
 $21,334/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -6632,7 +6632,7 @@
           <t>B | 267呎 (1房)
 $590万
 $22,104/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -6640,7 +6640,7 @@
           <t>C | 266呎 (1房)
 $609万
 $22,907/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -6648,7 +6648,7 @@
           <t>D | 252呎 (1房)
 $560万
 $22,206/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -6672,7 +6672,7 @@
           <t>B | 265呎 (1房)
 $603万
 $22,742/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -6680,7 +6680,7 @@
           <t>C | 266呎 (1房)
 $606万
 $22,794/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -6688,7 +6688,7 @@
           <t>D | 252呎 (1房)
 $557万
 $22,096/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -6704,7 +6704,7 @@
           <t>A | 189呎 (开放式)
 $388万
 $20,504/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -6712,7 +6712,7 @@
           <t>B | 196呎 (开放式)
 $358万
 $18,286/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -6720,7 +6720,7 @@
           <t>C | 248呎 (1房)
 $560万
 $22,576/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -6728,7 +6728,7 @@
           <t>D | 267呎 (1房)
 $591万
 $22,125/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -6736,7 +6736,7 @@
           <t>E | 252呎 (1房)
 $540万
 $21,447/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
           <t>A | 189呎 (开放式)
 $367万
 $19,417/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -6759,7 +6759,7 @@
           <t>B | 196呎 (开放式)
 $353万
 $18,017/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -6767,7 +6767,7 @@
           <t>C | 248呎 (1房)
 $552万
 $22,242/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -6775,7 +6775,7 @@
           <t>D | 267呎 (1房)
 $582万
 $21,798/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -6783,7 +6783,7 @@
           <t>E | 252呎 (1房)
 $532万
 $21,131/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
           <t>C | 248呎 (1房)
 $514万
 $20,723/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -6822,7 +6822,7 @@
           <t>D | 267呎 (1房)
 $530万
 $19,857/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -6830,7 +6830,7 @@
           <t>E | 252呎 (1房)
 $485万
 $19,249/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
           <t>B | 283呎 (1房)
 $577万
 $20,390/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -6877,7 +6877,7 @@
           <t>E | 268呎 (1房)
 $590万
 $22,030/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
           <t>A | 201呎 (开放式)
 $373万
 $18,569/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -6900,7 +6900,7 @@
           <t>B | 283呎 (1房)
 $602万
 $21,271/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -6908,7 +6908,7 @@
           <t>C | 264呎 (1房)
 $562万
 $21,271/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -6916,7 +6916,7 @@
           <t>D | 266呎 (1房)
 $554万
 $20,845/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -6924,7 +6924,7 @@
           <t>E | 268呎 (1房)
 $542万
 $20,207/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -6939,7 +6939,7 @@
           <t>A | 203呎 (开放式)
 $355万
 $17,493/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -6947,7 +6947,7 @@
           <t>B | 283呎 (1房)
 $548万
 $19,377/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -6955,7 +6955,7 @@
           <t>C | 282呎 (1房)
 $546万
 $19,377/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -6963,7 +6963,7 @@
           <t>D | 267呎 (1房)
 $507万
 $18,990/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -6971,7 +6971,7 @@
           <t>E | 304呎 (1房)
 $579万
 $19,036/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
           <t>A | 203呎 (开放式)
 $346万
 $17,045/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -6994,7 +6994,7 @@
           <t>B | 283呎 (1房)
 $540万
 $19,090/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -7002,7 +7002,7 @@
           <t>C | 282呎 (1房)
 $538万
 $19,091/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -7010,7 +7010,7 @@
           <t>D | 267呎 (1房)
 $500万
 $18,709/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -7018,7 +7018,7 @@
           <t>E | 304呎 (1房)
 $564万
 $18,548/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7033,7 @@
           <t>A | 203呎 (开放式)
 $340万
 $16,739/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -7041,7 +7041,7 @@
           <t>B | 283呎 (1房)
 $532万
 $18,808/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7049,7 +7049,7 @@
           <t>C | 282呎 (1房)
 $530万
 $18,809/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -7057,7 +7057,7 @@
           <t>D | 267呎 (1房)
 $492万
 $18,433/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -7065,7 +7065,7 @@
           <t>E | 304呎 (1房)
 $589万
 $19,371/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
           <t>C | 282呎 (1房)
 $621万
 $22,008/呎
-(26年-07月)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -7127,7 +7127,7 @@
           <t>A | 203呎 (开放式)
 $325万
 $15,988/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -7135,7 +7135,7 @@
           <t>B | 283呎 (1房)
 $521万
 $18,396/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -7143,7 +7143,7 @@
           <t>C | 282呎 (1房)
 $519万
 $18,396/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -7151,7 +7151,7 @@
           <t>D | 267呎 (1房)
 $481万
 $18,028/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -7159,7 +7159,7 @@
           <t>E | 304呎 (1房)
 $531万
 $17,476/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
           <t>A | 166呎 (开放式)
 $426万
 $25,688/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -7190,7 +7190,7 @@
           <t>C | 244呎 (1房)
 $572万
 $23,425/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -7198,7 +7198,7 @@
           <t>D | 229呎 (1房)
 $553万
 $24,130/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">

--- a/files/九龙-红磡-悦麓.xlsx
+++ b/files/九龙-红磡-悦麓.xlsx
@@ -5382,12 +5382,12 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7099,12 +7099,12 @@
 (26年-07月-17日)</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 267呎 (1房)
 $586万
 $21,936/呎
-(在售)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
